--- a/data/seed/portfolio/L-2025-0315/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-0315/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,28 +535,28 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>5680000</v>
+        <v>14055000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,152 +566,157 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SHARTNOMA №246/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за товар подог. №294/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72080000</v>
+        <v>80455000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>652000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>6673000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
+          <t>Mehnat Yog'och MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>251966368</t>
+          <t>263747928</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>20208000028355367001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1865</t>
+          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>71428000</v>
+        <v>87128000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>1486000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>3871000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №214/26</t>
+          <t>Оплата за продукцию по дог. №7/26, НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>69942000</v>
+        <v>90999000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>17002000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>3580000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №1664</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>52940000</v>
+        <v>94579000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>5832000</v>
+        <v>2043000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -721,37 +726,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №819 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5617</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58772000</v>
+        <v>96622000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>3603000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>2751000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -761,171 +766,166 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9025 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №130/26</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>62375000</v>
+        <v>93871000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1516000</v>
+        <v>17002000</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tong Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>324221629</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000181603590001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>60859000</v>
+        <v>76869000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>4230000</v>
+        <v>1224000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3058 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2730 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>65089000</v>
+        <v>78093000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>13020000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>1838000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №112/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №8306</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>78109000</v>
+        <v>76255000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>8597000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>1516000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>359556284</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000573828928001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6666 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>BINO IJARASI UCHUN TO'LOV IYUL</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>86706000</v>
+        <v>74739000</v>
       </c>
     </row>
     <row r="18">
@@ -937,221 +937,221 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>5825000</v>
+        <v>24144000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nurafshon Trans Servis MChJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>306698323</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000534657886001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №104/26, НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>92531000</v>
+        <v>98883000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>2401000</v>
+        <v>2972000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jizzax Moy MChJ</t>
+          <t>Mehnat Yog'och MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>393151657</t>
+          <t>263747928</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000805347025001</t>
+          <t>20208000028355367001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6507</t>
+          <t>Предоплата за товар по договору №18/26 от 09.07.2026</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>94932000</v>
+        <v>101855000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>658000</v>
+        <v>2427000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №113/26</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3819</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>94274000</v>
+        <v>99428000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2318000</v>
+        <v>3102000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Оплата за ырье по договору №137/26 от 09.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>91956000</v>
+        <v>96326000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>2318000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>5739000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Предоплата за товар по договору №235/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>89638000</v>
+        <v>102065000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>37517000</v>
+        <v>4621000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8915</t>
+          <t>Оплата за товар по счет-фактуре №1271 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>127155000</v>
+        <v>106686000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>8846000</v>
+        <v>1926000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1201,37 +1201,37 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2628</t>
+          <t>Предоплата за товар по дог. №28/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>136001000</v>
+        <v>108612000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>2396000</v>
+        <v>1633000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1241,77 +1241,77 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №69/26 от 15.07.2026</t>
+          <t>Оплата по счет-фактуре №7082 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>138397000</v>
+        <v>110245000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>5148000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>1963000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №63/26</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>143545000</v>
+        <v>108282000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>8052000</v>
+        <v>6437000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1321,37 +1321,37 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9660 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7381</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>151597000</v>
+        <v>114719000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>7200000</v>
+        <v>6254000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>369832345</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000465788620001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1361,192 +1361,197 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №287/26 от 20.07.2026</t>
+          <t>Оплата за продукцию по дог. №126/26, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>158797000</v>
+        <v>120973000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>3493000</v>
+        <v>2473000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №321 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8515 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>162290000</v>
+        <v>123446000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>31400000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>1675000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>369832345</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16307000295518829417</t>
+          <t>20208000465788620001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №40/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>130890000</v>
+        <v>125121000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>1507000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>1500000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №214/26</t>
+          <t>Оплата по счет-фактуре №8552 за поставленный товар</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>129383000</v>
+        <v>126621000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46225</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>2478000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>12805000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Предоплата за товар по дог. №84/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>126905000</v>
+        <v>139426000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>21555000</v>
+        <v>3028000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,317 +1561,317 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8716 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №209/26, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>148460000</v>
+        <v>142454000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>3797000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>2318000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6522 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>152257000</v>
+        <v>140136000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>948000</v>
+        <v>2318000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000771869892001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>151309000</v>
+        <v>137818000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>13214000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>1716000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №213/26 от 23.07.2026, НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №117/26 ОТ 15.07.2026</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>138095000</v>
+        <v>139534000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>681000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>1671000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №87/26</t>
+          <t>Оплата за товар по счет-фактуре №5679 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>137414000</v>
+        <v>141205000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5240000</v>
+        <v>6266000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldinda to'lov, shartnoma №24/26</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №82/26</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>132174000</v>
+        <v>134939000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>17431000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>57296000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200474367</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000962160529001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5447 27.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №1320</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>149605000</v>
+        <v>77643000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>14617000</v>
+        <v>1966000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Shartnoma №133/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №117/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>164222000</v>
+        <v>79609000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>2722000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>1004000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Mehnat Yog'och MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>263747928</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000028355367001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,197 +1881,192 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8352</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>161500000</v>
+        <v>80613000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3557000</v>
+        <v>1900000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №226/26 ОТ 27.07.2026, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3195</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>157943000</v>
+        <v>78713000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>106654000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>17006000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №164/26</t>
+          <t>Оплата за товар по счет-фактуре №571 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>51289000</v>
+        <v>95719000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46231</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>15026000</v>
+        <v>6319000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7711 за посавленный товар</t>
+          <t>Предоплата за товар по дог. №250/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>66315000</v>
+        <v>102038000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46231</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>4206000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>2116000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №232/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4508</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>70521000</v>
+        <v>99922000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46231</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>5141000</v>
+        <v>31400000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>266684342</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>16307000295518829417</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2076,432 +2076,437 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6313</t>
+          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>65380000</v>
+        <v>68522000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>5209000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>32924000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №110/26 от 30.07.2026</t>
+          <t>Оплата за сырье по дог. №237/26 от 2.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>70589000</v>
+        <v>35598000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46233</v>
+        <v>46224</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>2784000</v>
+        <v>3179000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №229/26 от 30.07.2026</t>
+          <t>Предоплата за товар по договору №282/26 от 21.07.2026</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>73373000</v>
+        <v>38777000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46233</v>
+        <v>46224</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1632000</v>
+        <v>2509000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №139/26 от 30.07.2026, НДС 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>71741000</v>
+        <v>36268000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46233</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>8427000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>1165000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №121/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1511</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63314000</v>
+        <v>37433000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>5176000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Toshkent Mebel XK</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №26/26, НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>63014000</v>
+        <v>42609000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>865000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>3185000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №10/26</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №8427 23.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>62149000</v>
+        <v>45794000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>18159000</v>
+        <v>2071000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №87/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №3950 ОТ 23.07.206, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>80308000</v>
+        <v>47865000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>11530000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>7922000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №554 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №8991</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>91838000</v>
+        <v>39943000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46237</v>
+        <v>46227</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>3447000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>4076000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №80/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №73/26</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>95285000</v>
+        <v>35867000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>1114000</v>
+        <v>5689000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №73/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №140/26, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>96399000</v>
+        <v>41556000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>14565000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>1702000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2511,237 +2516,237 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7374</t>
+          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>81834000</v>
+        <v>43258000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>16850000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>1523000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Omad Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>215165758</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000534702570001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №153/26 от 03.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>64984000</v>
+        <v>44781000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>3415000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>948000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000581997813001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9906 за поставленный товар</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>68399000</v>
+        <v>43833000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46238</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>2756000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>4838000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1608 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №511</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>71155000</v>
+        <v>38995000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>13213000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>5224000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>221629018</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000603590777001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №255/26 от 05.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №116/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>84368000</v>
+        <v>33771000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46239</v>
+        <v>46231</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>8464000</v>
+        <v>29515000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №221/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3282 за поставленный товар</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>92832000</v>
+        <v>63286000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46239</v>
+        <v>46231</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>3424000</v>
+        <v>4037000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2751,192 +2756,197 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3776 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Предолата за товар по договору №223/26 от 28.07.2026</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>96256000</v>
+        <v>67323000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46240</v>
+        <v>46231</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>17788000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>8636000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shartnoma №239/2 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №180/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>114044000</v>
+        <v>58687000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>4017000</v>
+        <v>11044000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Omad Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>215165758</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000534702570001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №135/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №6132 за поставленный товар</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>118061000</v>
+        <v>69731000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46240</v>
+        <v>46233</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>16752000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>2047000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Toshkent Mebel XK</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Предоплата за товар по дог. №145/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>101309000</v>
+        <v>71778000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>1494000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>1309000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tong Qurilish AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>324221629</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000181603590001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по дог. №42/20</t>
+          <t>Оплата за товар по счет-фактуре №9353 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>99815000</v>
+        <v>73087000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>18522000</v>
+        <v>1101000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2946,157 +2956,152 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov,shartn. №134/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №639</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>118337000</v>
+        <v>74188000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>5094000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>273005106</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8702 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>123431000</v>
+        <v>73888000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>2273000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>11477000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jizzax Moy MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>393151657</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000805347025001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №261/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>125704000</v>
+        <v>62411000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>1256000</v>
+        <v>3727000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №227/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №5256 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>126960000</v>
+        <v>66138000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>1202000</v>
+        <v>3408000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3106,37 +3111,37 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7265за поставленный товар</t>
+          <t>Shartnom №193/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>128162000</v>
+        <v>69546000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>1133000</v>
+        <v>3274000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3146,77 +3151,77 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>129295000</v>
+        <v>72820000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>5165000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>1294000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №132/26 от 10.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №202/26, QQS 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>124130000</v>
+        <v>74114000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>1025000</v>
+        <v>1191000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3226,277 +3231,272 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2716 ОТ 11.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по с/ф №3349 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>125155000</v>
+        <v>75305000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>4309000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №231/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8960</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>129464000</v>
+        <v>71805000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>1050000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>3922000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>221629018</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000603590777001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №180/26 ОТ 12.08.2026</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6700</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>130514000</v>
+        <v>67883000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>41439000</v>
+        <v>1210000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3679 от 13.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7334 05.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>171953000</v>
+        <v>69093000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>1078000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>3646000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2862 13.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №824</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>173031000</v>
+        <v>65447000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>987000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>16752000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>273005106</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4030 за поставленный товар</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №1935</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>174018000</v>
+        <v>48695000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46247</v>
+        <v>46240</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>2806000</v>
+        <v>4220000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>251966368</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8121</t>
+          <t>Предоплата за материалы по договору №85/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>171212000</v>
+        <v>44475000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>1711000</v>
+        <v>2902000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3506,197 +3506,197 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №104/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7057 07.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>172923000</v>
+        <v>47377000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>1173000</v>
+        <v>2814000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Omad Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>215165758</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000534702570001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №289/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №78/26, НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>174096000</v>
+        <v>50191000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>2284000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>5738000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Logistik MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>388336538</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000806317065001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата по счет-фактуре №4681 за поставленный товар</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>171812000</v>
+        <v>55929000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>2284000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>2805000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №570 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>169528000</v>
+        <v>58734000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>13343000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>2426000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №50/26 от 18.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2008 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>156185000</v>
+        <v>61160000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>3339000</v>
+        <v>1370000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3706,352 +3706,357 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5769</t>
+          <t>Mahsulot uchun to'lov, shartnoma №157/26, QQS 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>159524000</v>
+        <v>62530000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>1303000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>1494000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>359556284</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000573828928001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5665 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за август, дог. №84/21</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>160827000</v>
+        <v>61036000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>31400000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>3029000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
+          <t>Shodlik Non XK</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>16307000295518829417</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по счет-фактуре №7133 за поставленный товар</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>129427000</v>
+        <v>64065000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46255</v>
+        <v>46245</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>4442000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>5107000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>221629018</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000603590777001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6357 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №91/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>133869000</v>
+        <v>58958000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46255</v>
+        <v>46245</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>4409000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>8797000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2427 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>138278000</v>
+        <v>50161000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>2445000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>4476000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата по счет-фактуре №6144 за поставленный товар</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>135833000</v>
+        <v>54637000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>3961000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>4016000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №176/26</t>
+          <t>Предоплата за товар по договору №114/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>131872000</v>
+        <v>58653000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>5738000</v>
+        <v>15811000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно чет-фактуре №1226</t>
+          <t>Предоплата за материалы по договоу №33/26</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>126134000</v>
+        <v>42842000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>4714000</v>
+        <v>3453000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4772</t>
+          <t>Оплата за товар по счет-фактуре №9553 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>130848000</v>
+        <v>46295000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>3565000</v>
+        <v>1217000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4061,117 +4066,117 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №22/26, QQS 12%</t>
+          <t>Shartnoma №283/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>134413000</v>
+        <v>47512000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>3553000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>2284000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №174/26 ОТ 24.08.2026</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>137966000</v>
+        <v>45228000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>4871000</v>
+        <v>2284000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2206</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>133095000</v>
+        <v>42944000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>42159000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>32537000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>369832345</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000465788620001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4181,37 +4186,37 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №246/26</t>
+          <t>Оплата по с/ф №9513 за поставленный товар</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>90936000</v>
+        <v>75481000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>4398000</v>
+        <v>15641000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4221,37 +4226,37 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №119/26 от 26.08.2026</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1279 ОТ 18.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>95334000</v>
+        <v>91122000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>1891000</v>
+        <v>4105000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,157 +4266,157 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8743 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №2/26, НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>97225000</v>
+        <v>95227000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>13628000</v>
+        <v>3783000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Gulshan Sut AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>341049260</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000176882557001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №124/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8353</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>83597000</v>
+        <v>91444000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>934000</v>
+        <v>62011000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000771869892001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchn to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №2995</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>82663000</v>
+        <v>29433000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>1302000</v>
+        <v>6899000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>83965000</v>
+        <v>36332000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>21572000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>1720000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4421,232 +4426,232 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №154/26</t>
+          <t>Оплата за продукцию по договору №140/26, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>62393000</v>
+        <v>38052000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>1217000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>4032000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5352 за поставленный товар</t>
+          <t>Оплата за сырье по договору №277/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>63610000</v>
+        <v>34020000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>300000</v>
+        <v>5964000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Оплата за товары согласно счет-фактуре №8794</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>63310000</v>
+        <v>28056000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>3171000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>2391000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6112</t>
+          <t>Предоплата за товар по договору №235/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>60139000</v>
+        <v>30447000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>6714000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1310000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2766</t>
+          <t>Оплата по счет-фактуре №7370 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>53425000</v>
+        <v>31757000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46266</v>
+        <v>46254</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>13531000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>31400000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>273005106</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>16307000295518829417</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2581 от 01.09.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>66956000</v>
+        <v>357000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46266</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>2498000</v>
+        <v>42765000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4656,197 +4661,197 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6693 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №3626 от 21.08.2026, в т.ч НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>69454000</v>
+        <v>43122000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46266</v>
+        <v>46255</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>2202000</v>
+        <v>22861000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплта за товар по счет-фактуре №6538 от 01.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>71656000</v>
+        <v>65983000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46267</v>
+        <v>46255</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>2143000</v>
+        <v>1244000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Omad Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>215165758</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000534702570001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2754 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №9862 за поставленный товар</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>73799000</v>
+        <v>67227000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>7590000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>16270000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navoiy Plastik MChJ</t>
+          <t>Bekobod Logistik XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>322593493</t>
+          <t>217844471</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000093840306001</t>
+          <t>20208000917578563001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA№235/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №2682</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>81389000</v>
+        <v>50957000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>4205000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>2490000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6548 за поставленный товар</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>85594000</v>
+        <v>48467000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>11648000</v>
+        <v>13065000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4856,77 +4861,77 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8301 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8619 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>97242000</v>
+        <v>61532000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>11506000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>19831000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2816 за поставленный товар</t>
+          <t>Предоплата за материалы по дог. №230/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>108748000</v>
+        <v>41701000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>9998000</v>
+        <v>2619000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4936,117 +4941,117 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №261</t>
+          <t>Оплата за товар по счет-фактуре №805 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>118746000</v>
+        <v>44320000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>3019000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>934000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000581997813001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №234/26 от 07.09.2026</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>121765000</v>
+        <v>43386000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>2694000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>1359000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8668</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №278/26, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>119071000</v>
+        <v>44745000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>2697000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>5437000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ziyo Meva Eksport AJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>249264356</t>
+          <t>369832345</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000105688685001</t>
+          <t>20208000465788620001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5056,152 +5061,152 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №205/26</t>
+          <t>Оплата по с/ф №6204 за поставленный товар</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>116374000</v>
+        <v>50182000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>13920000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>3069000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>251966368</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7784</t>
+          <t>Оплата за товар по счет-фактуре №8913 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>102454000</v>
+        <v>53251000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>16836000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>2141000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Shodlik Non XK</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №7779</t>
+          <t>Оплата за товар по счет-фактуре №4595 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>85618000</v>
+        <v>55392000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>40579000</v>
+        <v>300000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>251966368</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №279/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>45039000</v>
+        <v>55092000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>1933000</v>
+        <v>2787000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5211,117 +5216,117 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9100 от 08.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5516 за поставленный товар</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46972000</v>
+        <v>57879000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>1501000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>2292000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tong Qurilish AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>324221629</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000181603590001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №42/20</t>
+          <t>Оплата за продукцию по договору №290/26, НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>45471000</v>
+        <v>60171000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>2403000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>3837000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4471 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №296/26, QQS bilan</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>47874000</v>
+        <v>56334000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>1994000</v>
+        <v>9873000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5331,117 +5336,117 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №259/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3915 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>49868000</v>
+        <v>66207000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>1860000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>45566000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №284/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №250/26</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>51728000</v>
+        <v>20641000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>37085000</v>
+        <v>5156000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jizzax Moy MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>393151657</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000805347025001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5861 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1203 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>88813000</v>
+        <v>25797000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46275</v>
+        <v>46269</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>3964000</v>
+        <v>2133000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5451,77 +5456,77 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4743 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №8746 за поставленный товар</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>92777000</v>
+        <v>27930000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46275</v>
+        <v>46269</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>1505000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>1528000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>221629018</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000603590777001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №233/26 от 10.09.2026</t>
+          <t>Предоплата за материалы по дог. №47/26</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>94282000</v>
+        <v>26402000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>11035000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>4099000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5531,77 +5536,77 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №123/26</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>105317000</v>
+        <v>22303000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>7392000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>4392000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>350637479</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000840283553001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Shartnoma №147/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №9929</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>112709000</v>
+        <v>17911000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>2042000</v>
+        <v>6233000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5611,392 +5616,392 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №297/26, НДС 12%</t>
+          <t>Оплата п счет-фактуре №1816 за поставленный товар</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>114751000</v>
+        <v>24144000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>1696000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>5519000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2623</t>
+          <t>Оплата за продукцию по договору №142/26, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>113055000</v>
+        <v>29663000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>50003000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>4240000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5103</t>
+          <t>Оплата по счет-фактуре №5932 за поставленный товар</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>63052000</v>
+        <v>33903000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>2000000</v>
+        <v>2416000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6284 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2231 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>65052000</v>
+        <v>36319000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>1356000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>16836000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>279583684</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №88/26 от 15.09.2026</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №4274</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>66408000</v>
+        <v>19483000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>2296000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>12027000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Shartnoma №237/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>64112000</v>
+        <v>31510000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>2296000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>2535000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>SHARTNOMA №156/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>61816000</v>
+        <v>34045000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>8272000</v>
+        <v>1851000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>296636896</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000362753562001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8801 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №245 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>70088000</v>
+        <v>35896000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46285</v>
+        <v>46274</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>31400000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>12249000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>16307000295518829417</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №3284 за поставленный товар</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>38688000</v>
+        <v>48145000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>25863000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>1501000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>359556284</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000573828928001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1650 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>64551000</v>
+        <v>46644000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>3641000</v>
+        <v>6835000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,277 +6011,277 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №256/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №62/26 от 10.09.2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>68192000</v>
+        <v>53479000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>3244000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>3888000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Nihol Mebel MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200474367</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000962160529001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №208/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №231/26</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>71436000</v>
+        <v>49591000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>2593000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>10441000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №31/26</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>74029000</v>
+        <v>39150000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>1810000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>6907000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Toshkent Mebel XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>358368453</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000233724747001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №26/26</t>
+          <t>Shartnoma №142/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>72219000</v>
+        <v>46057000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1965000</v>
+        <v>8590000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3762</t>
+          <t>Xom ashyo uchun to'lov, shartn. №291/26, QQS bilan</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>70254000</v>
+        <v>37467000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>2466000</v>
+        <v>11034000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №183/26</t>
+          <t>Оплата за транспортные услуги по договору №83/26</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>67788000</v>
+        <v>26433000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>4155000</v>
+        <v>2887000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №917</t>
+          <t>Оплата за товары согласно с/ф №162</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>63633000</v>
+        <v>23546000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>8973000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>14835000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,237 +6291,237 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1494 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №935</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>72606000</v>
+        <v>8711000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>2513000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>2461000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Предоплата за товар по договору №6/26 от 16.09.2026</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>70093000</v>
+        <v>11172000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>3350000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>2138000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2707</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №169/26, НДС 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>66743000</v>
+        <v>13310000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>5141000</v>
+        <v>2296000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>251966368</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №42/26</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>61602000</v>
+        <v>11014000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>4532000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>2296000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>279583684</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000352337247001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №107/26 от 23.09.2026</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>66134000</v>
+        <v>8718000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>2754000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>14274000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7774 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №200/26</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>68888000</v>
+        <v>-5556000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>2002000</v>
-      </c>
+      <c r="C158" s="2" t="n">
+        <v>1937000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Yangi Hayot Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>368434232</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000412582643001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6526,77 +6531,72 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6052 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №48/26</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>70890000</v>
+        <v>-7493000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>938000</v>
+        <v>31400000</v>
       </c>
       <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>200933985</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0315)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000771869892001</t>
+          <t>16307000295518829417</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Kredit shartnomasi L-2025-0315 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>69952000</v>
+        <v>-38893000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>1552000</v>
+        <v>7087000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6606,317 +6606,317 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6753 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>71504000</v>
+        <v>-31806000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>4780000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>6423000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Afrosiyob Logistik MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>251966368</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000683627535001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №41/26 от 24.09.2026, НДС 12%</t>
+          <t>Оплата за товар по с/ф №1798 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>66724000</v>
+        <v>-25383000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>5897000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>5443000</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №44/26</t>
+          <t>Предоплата за товар по договору №179/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>60827000</v>
+        <v>-19940000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>3723000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>259349320</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000384030687001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6834</t>
+          <t>Предоплата за товар по договору №94/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>54927000</v>
+        <v>-16217000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>2105000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>2621000</v>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Urganch Meva-Sabzavot AJ</t>
+          <t>Omad Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>215883365</t>
+          <t>215165758</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000828063170001</t>
+          <t>20208000534702570001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5337</t>
+          <t>Оплата по счет-фактуре №6578 за поставленный товар</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>52822000</v>
+        <v>-13596000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>3807000</v>
+        <v>10703000</v>
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Denov Non MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>326435621</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000568868544001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №161/26</t>
+          <t>Оплата за транспортные услуги по договору №226/26</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>49015000</v>
+        <v>-24299000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
-      <c r="C166" s="2" t="n">
-        <v>1590000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>7430000</v>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>266684342</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000224125826001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №277/26</t>
+          <t>Оплата за товар по счет-фактуре №1464 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>47425000</v>
+        <v>-16869000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>1647000</v>
-      </c>
+      <c r="C167" s="2" t="n">
+        <v>2521000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3989 за поставленный товар</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>49072000</v>
+        <v>-19390000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>1428000</v>
+        <v>26729000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chirchiq Sut MChJ</t>
+          <t>Shodlik Non XK</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>273005106</t>
+          <t>200510632</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000221495458001</t>
+          <t>20208000149545809001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6926,71 +6926,431 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9744 за поставленный товар</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №100/26, QQS 12%</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>50500000</v>
+        <v>7339000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>2271000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>259349320</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000384030687001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №1470 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>9610000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>938000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000581997813001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>8672000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>14476000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Omad Dori-Darmon AJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>215165758</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000534702570001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>23148000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>6520000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Shodlik Non XK</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>200510632</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000149545809001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Shartnoma №160/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>29668000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>2311000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Shodlik Non XK</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>200510632</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000149545809001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №155/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>31979000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>12808000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Yangi Hayot Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>368434232</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000412582643001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №289/26</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>19171000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>14006000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Toshkent Mebel XK</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>358368453</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000233724747001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №56/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>33177000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>23410000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Toshkent Mebel XK</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>358368453</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000233724747001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №276/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>56587000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
         <is>
           <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Комиссия за перевод</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>56287000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>6087000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Denov Non MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>326435621</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000568868544001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №53/26</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
         <v>50200000</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C170" s="4" t="n">
-        <v>635787000</v>
-      </c>
-      <c r="D170" s="4" t="n">
-        <v>619587000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="C179" s="4" t="n">
+        <v>642893000</v>
+      </c>
+      <c r="D179" s="4" t="n">
+        <v>626693000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C180" s="4" t="n">
         <v>50200000</v>
       </c>
-      <c r="D171" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
